--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/11.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/11.xlsx
@@ -426,13 +426,13 @@
         <v>-17.75244347529873</v>
       </c>
       <c r="E2">
-        <v>-20.6052516681309</v>
+        <v>-19.09804419263198</v>
       </c>
       <c r="F2">
-        <v>-0.1002615958453459</v>
+        <v>0.9667700528443365</v>
       </c>
       <c r="G2">
-        <v>-13.45924817054631</v>
+        <v>-8.487039236777086</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.50640224839509</v>
       </c>
       <c r="E3">
-        <v>-21.90789438728133</v>
+        <v>-19.21428559193487</v>
       </c>
       <c r="F3">
-        <v>-0.402369672748534</v>
+        <v>0.4841267558076213</v>
       </c>
       <c r="G3">
-        <v>-13.66485607590424</v>
+        <v>-8.408857570680198</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.23910147176196</v>
       </c>
       <c r="E4">
-        <v>-21.62414926290872</v>
+        <v>-18.09436227051994</v>
       </c>
       <c r="F4">
-        <v>-0.2546825336056185</v>
+        <v>0.7781441682876666</v>
       </c>
       <c r="G4">
-        <v>-13.2611641062242</v>
+        <v>-7.111121319033574</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.9757328002829</v>
       </c>
       <c r="E5">
-        <v>-22.47152637617201</v>
+        <v>-19.32214931432357</v>
       </c>
       <c r="F5">
-        <v>-0.4329206909311826</v>
+        <v>0.8457472320301342</v>
       </c>
       <c r="G5">
-        <v>-12.80732850867272</v>
+        <v>-9.008195657063689</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.70993281917096</v>
       </c>
       <c r="E6">
-        <v>-22.86331636189363</v>
+        <v>-19.07300173136957</v>
       </c>
       <c r="F6">
-        <v>-0.2075600255299659</v>
+        <v>0.8897351978535937</v>
       </c>
       <c r="G6">
-        <v>-12.43322331379419</v>
+        <v>-8.230949737727105</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.45944005380671</v>
       </c>
       <c r="E7">
-        <v>-23.35783025200524</v>
+        <v>-20.04325445835699</v>
       </c>
       <c r="F7">
-        <v>-0.3730802581203491</v>
+        <v>0.5412575988438976</v>
       </c>
       <c r="G7">
-        <v>-12.45936808717985</v>
+        <v>-7.347497238954412</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.23344059381565</v>
       </c>
       <c r="E8">
-        <v>-22.97799996613788</v>
+        <v>-21.34295819787643</v>
       </c>
       <c r="F8">
-        <v>0.1193932748853878</v>
+        <v>1.661770303793122</v>
       </c>
       <c r="G8">
-        <v>-12.29646199919653</v>
+        <v>-7.126736652434971</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.02274434254828</v>
       </c>
       <c r="E9">
-        <v>-24.2275055712823</v>
+        <v>-22.00548300214662</v>
       </c>
       <c r="F9">
-        <v>-0.0485151409272664</v>
+        <v>0.8255185000537704</v>
       </c>
       <c r="G9">
-        <v>-12.32101538012586</v>
+        <v>-8.044123544575442</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.81089007238316</v>
       </c>
       <c r="E10">
-        <v>-25.0862853820969</v>
+        <v>-22.10686647823035</v>
       </c>
       <c r="F10">
-        <v>0.4308817842578775</v>
+        <v>1.038032843772372</v>
       </c>
       <c r="G10">
-        <v>-12.19898346910855</v>
+        <v>-7.396118380022264</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.60205118896014</v>
       </c>
       <c r="E11">
-        <v>-25.29009841176012</v>
+        <v>-22.10839710244494</v>
       </c>
       <c r="F11">
-        <v>0.4522776859047859</v>
+        <v>1.277908162805442</v>
       </c>
       <c r="G11">
-        <v>-11.88086575769883</v>
+        <v>-7.951166537796373</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.3841525659889</v>
       </c>
       <c r="E12">
-        <v>-25.65923244202137</v>
+        <v>-24.33483493373809</v>
       </c>
       <c r="F12">
-        <v>0.5569733852098099</v>
+        <v>2.089958384504603</v>
       </c>
       <c r="G12">
-        <v>-11.10136892037246</v>
+        <v>-8.095983251322465</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.13162968312462</v>
       </c>
       <c r="E13">
-        <v>-26.36022663298671</v>
+        <v>-23.64427434688642</v>
       </c>
       <c r="F13">
-        <v>0.6575686658709762</v>
+        <v>2.277686318796638</v>
       </c>
       <c r="G13">
-        <v>-11.01045283340337</v>
+        <v>-8.53328805465746</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.85777035569686</v>
       </c>
       <c r="E14">
-        <v>-27.3471079165303</v>
+        <v>-23.7021799440225</v>
       </c>
       <c r="F14">
-        <v>0.8022794809356331</v>
+        <v>2.994547185505302</v>
       </c>
       <c r="G14">
-        <v>-10.33339245194131</v>
+        <v>-6.644347864873207</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.56438265740499</v>
       </c>
       <c r="E15">
-        <v>-27.87437173066538</v>
+        <v>-26.52867680912404</v>
       </c>
       <c r="F15">
-        <v>1.065402102760868</v>
+        <v>1.90663405132585</v>
       </c>
       <c r="G15">
-        <v>-10.0466005627596</v>
+        <v>-7.054021501456117</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.245760221118</v>
       </c>
       <c r="E16">
-        <v>-28.04892176129104</v>
+        <v>-25.80173899056874</v>
       </c>
       <c r="F16">
-        <v>1.033269731206275</v>
+        <v>3.284018517678784</v>
       </c>
       <c r="G16">
-        <v>-9.713760010212647</v>
+        <v>-7.64248890081317</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.91363416217934</v>
       </c>
       <c r="E17">
-        <v>-29.17775259107906</v>
+        <v>-25.66470283862263</v>
       </c>
       <c r="F17">
-        <v>1.368241628080728</v>
+        <v>3.61017658538745</v>
       </c>
       <c r="G17">
-        <v>-9.241956443401651</v>
+        <v>-7.646711832960175</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.58514954049257</v>
       </c>
       <c r="E18">
-        <v>-29.78501189855964</v>
+        <v>-28.40915734012721</v>
       </c>
       <c r="F18">
-        <v>1.709817269890299</v>
+        <v>3.208338871759021</v>
       </c>
       <c r="G18">
-        <v>-9.088733240240261</v>
+        <v>-6.6722776227872</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.26425955462173</v>
       </c>
       <c r="E19">
-        <v>-30.29681097395853</v>
+        <v>-28.90321385436404</v>
       </c>
       <c r="F19">
-        <v>1.794193116804651</v>
+        <v>3.677789589538751</v>
       </c>
       <c r="G19">
-        <v>-8.207141194091774</v>
+        <v>-7.978663174464519</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.94723585217136</v>
       </c>
       <c r="E20">
-        <v>-31.57004125442913</v>
+        <v>-28.80316174963857</v>
       </c>
       <c r="F20">
-        <v>1.951632625380725</v>
+        <v>4.298914378771071</v>
       </c>
       <c r="G20">
-        <v>-8.551692426384385</v>
+        <v>-6.011597099349888</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.65307451914368</v>
       </c>
       <c r="E21">
-        <v>-32.00927832656611</v>
+        <v>-29.40945649215552</v>
       </c>
       <c r="F21">
-        <v>2.260626920503385</v>
+        <v>4.122970799151261</v>
       </c>
       <c r="G21">
-        <v>-7.988306684627727</v>
+        <v>-5.86787303260309</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.3835063886921</v>
       </c>
       <c r="E22">
-        <v>-32.77563877559518</v>
+        <v>-31.05895088521244</v>
       </c>
       <c r="F22">
-        <v>2.339460989493008</v>
+        <v>4.341764167783084</v>
       </c>
       <c r="G22">
-        <v>-8.514676965972289</v>
+        <v>-5.538881352945365</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.1265311937457</v>
       </c>
       <c r="E23">
-        <v>-32.7997981844261</v>
+        <v>-31.53035370822591</v>
       </c>
       <c r="F23">
-        <v>2.272716114379841</v>
+        <v>4.940803025321963</v>
       </c>
       <c r="G23">
-        <v>-8.226989303304855</v>
+        <v>-5.840179522641376</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.89538390561121</v>
       </c>
       <c r="E24">
-        <v>-33.84204685542447</v>
+        <v>-33.04423389017513</v>
       </c>
       <c r="F24">
-        <v>2.571400548807259</v>
+        <v>5.083671551282793</v>
       </c>
       <c r="G24">
-        <v>-7.783223774719313</v>
+        <v>-5.625581070210574</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.69441793591182</v>
       </c>
       <c r="E25">
-        <v>-33.51119201595007</v>
+        <v>-31.40586595775505</v>
       </c>
       <c r="F25">
-        <v>2.928600856568433</v>
+        <v>5.001071724080044</v>
       </c>
       <c r="G25">
-        <v>-8.3017683426446</v>
+        <v>-4.706212320248199</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.51707286584497</v>
       </c>
       <c r="E26">
-        <v>-34.36577393135956</v>
+        <v>-32.84601352591138</v>
       </c>
       <c r="F26">
-        <v>2.785382759563622</v>
+        <v>4.979007329939076</v>
       </c>
       <c r="G26">
-        <v>-7.70412008536422</v>
+        <v>-5.021255527056724</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.36390909603874</v>
       </c>
       <c r="E27">
-        <v>-34.25994575803731</v>
+        <v>-32.49654439402845</v>
       </c>
       <c r="F27">
-        <v>3.086141425967649</v>
+        <v>5.069294406639806</v>
       </c>
       <c r="G27">
-        <v>-7.723810695942448</v>
+        <v>-4.971042993532541</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.24426590855992</v>
       </c>
       <c r="E28">
-        <v>-34.29393421970187</v>
+        <v>-32.69571800207081</v>
       </c>
       <c r="F28">
-        <v>3.024375038945307</v>
+        <v>5.341037019658573</v>
       </c>
       <c r="G28">
-        <v>-8.015419418373419</v>
+        <v>-4.599356058943322</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.15458613875089</v>
       </c>
       <c r="E29">
-        <v>-35.03631639886033</v>
+        <v>-33.73512052715535</v>
       </c>
       <c r="F29">
-        <v>2.626969090921855</v>
+        <v>5.28007249228214</v>
       </c>
       <c r="G29">
-        <v>-7.875737816587857</v>
+        <v>-4.845467363231033</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.08012357931158</v>
       </c>
       <c r="E30">
-        <v>-34.09992307202826</v>
+        <v>-33.01230135571004</v>
       </c>
       <c r="F30">
-        <v>2.588696860177712</v>
+        <v>5.098136502870479</v>
       </c>
       <c r="G30">
-        <v>-8.040487951087576</v>
+        <v>-5.461037652669099</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.02905583443284</v>
       </c>
       <c r="E31">
-        <v>-33.86878749443976</v>
+        <v>-33.41069385653484</v>
       </c>
       <c r="F31">
-        <v>2.608841098678991</v>
+        <v>4.754870991559197</v>
       </c>
       <c r="G31">
-        <v>-8.035687523946109</v>
+        <v>-4.902324370413091</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.99368576786645</v>
       </c>
       <c r="E32">
-        <v>-33.93232651324139</v>
+        <v>-32.35811573632498</v>
       </c>
       <c r="F32">
-        <v>2.680329205540588</v>
+        <v>5.059425237402852</v>
       </c>
       <c r="G32">
-        <v>-7.744164113275684</v>
+        <v>-5.285685891310814</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.95505015114699</v>
       </c>
       <c r="E33">
-        <v>-34.05458851873748</v>
+        <v>-32.99901254873453</v>
       </c>
       <c r="F33">
-        <v>2.753914738666074</v>
+        <v>4.466029218611843</v>
       </c>
       <c r="G33">
-        <v>-8.146779842284229</v>
+        <v>-4.771485660730233</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.91119811559067</v>
       </c>
       <c r="E34">
-        <v>-33.8415374020986</v>
+        <v>-31.4560799417891</v>
       </c>
       <c r="F34">
-        <v>2.740718845939478</v>
+        <v>4.966972808311205</v>
       </c>
       <c r="G34">
-        <v>-8.03172052708074</v>
+        <v>-4.945364153608327</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.85819659049457</v>
       </c>
       <c r="E35">
-        <v>-33.64396008114394</v>
+        <v>-32.29223096798738</v>
       </c>
       <c r="F35">
-        <v>2.618403771976908</v>
+        <v>4.403742616860542</v>
       </c>
       <c r="G35">
-        <v>-8.046853520912899</v>
+        <v>-4.587783190503161</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.7846598068009</v>
       </c>
       <c r="E36">
-        <v>-33.6710267702878</v>
+        <v>-32.71852113293643</v>
       </c>
       <c r="F36">
-        <v>2.68512048259838</v>
+        <v>4.486594267753744</v>
       </c>
       <c r="G36">
-        <v>-7.928270173754567</v>
+        <v>-4.960109963296472</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.68362617164394</v>
       </c>
       <c r="E37">
-        <v>-32.81929326502912</v>
+        <v>-30.39582832237324</v>
       </c>
       <c r="F37">
-        <v>2.622828910642663</v>
+        <v>4.8057957060137</v>
       </c>
       <c r="G37">
-        <v>-7.983338915186728</v>
+        <v>-3.678212168117288</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.5640205274453</v>
       </c>
       <c r="E38">
-        <v>-32.56441489821841</v>
+        <v>-29.28986855056096</v>
       </c>
       <c r="F38">
-        <v>2.818878623863222</v>
+        <v>4.175262319820384</v>
       </c>
       <c r="G38">
-        <v>-7.626620913351696</v>
+        <v>-3.917216346507241</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.42779158855088</v>
       </c>
       <c r="E39">
-        <v>-32.48041849808713</v>
+        <v>-31.57627243466369</v>
       </c>
       <c r="F39">
-        <v>2.574675913517928</v>
+        <v>4.602202879223248</v>
       </c>
       <c r="G39">
-        <v>-7.720680410574738</v>
+        <v>-4.595579372928402</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.26915113561154</v>
       </c>
       <c r="E40">
-        <v>-32.4161639803923</v>
+        <v>-30.37008621187664</v>
       </c>
       <c r="F40">
-        <v>2.552469040183679</v>
+        <v>4.229515414499334</v>
       </c>
       <c r="G40">
-        <v>-8.225217443662755</v>
+        <v>-4.270285629968171</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.10606487810078</v>
       </c>
       <c r="E41">
-        <v>-31.57032881252862</v>
+        <v>-29.37311095976996</v>
       </c>
       <c r="F41">
-        <v>2.775657726254755</v>
+        <v>4.350533265109119</v>
       </c>
       <c r="G41">
-        <v>-7.612432911328656</v>
+        <v>-5.545220672998213</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.946674615128813</v>
       </c>
       <c r="E42">
-        <v>-31.64794912125709</v>
+        <v>-28.38189592660103</v>
       </c>
       <c r="F42">
-        <v>2.648947334852932</v>
+        <v>4.545767864805324</v>
       </c>
       <c r="G42">
-        <v>-8.063259628710123</v>
+        <v>-4.351597581432771</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.790010755271954</v>
       </c>
       <c r="E43">
-        <v>-30.99993128347047</v>
+        <v>-27.776144600965</v>
       </c>
       <c r="F43">
-        <v>2.595959985565459</v>
+        <v>4.891516821590198</v>
       </c>
       <c r="G43">
-        <v>-7.812200242310769</v>
+        <v>-4.584518375051513</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.646155967854472</v>
       </c>
       <c r="E44">
-        <v>-30.51308409985385</v>
+        <v>-28.59347981766141</v>
       </c>
       <c r="F44">
-        <v>2.690658947053498</v>
+        <v>4.575733227234193</v>
       </c>
       <c r="G44">
-        <v>-8.03077225405006</v>
+        <v>-3.936109620246524</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.526185320766309</v>
       </c>
       <c r="E45">
-        <v>-30.00548065562307</v>
+        <v>-27.87959306119623</v>
       </c>
       <c r="F45">
-        <v>2.695335909409704</v>
+        <v>4.154874541302681</v>
       </c>
       <c r="G45">
-        <v>-7.915909812140139</v>
+        <v>-4.443803188474726</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.430920561793073</v>
       </c>
       <c r="E46">
-        <v>-29.26996137882324</v>
+        <v>-26.36198368090169</v>
       </c>
       <c r="F46">
-        <v>2.413392780192864</v>
+        <v>4.547671453096957</v>
       </c>
       <c r="G46">
-        <v>-8.070363473386321</v>
+        <v>-4.60250275041883</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.356485893893188</v>
       </c>
       <c r="E47">
-        <v>-29.47601600312026</v>
+        <v>-27.62505206569908</v>
       </c>
       <c r="F47">
-        <v>2.767390619574816</v>
+        <v>4.133390004343673</v>
       </c>
       <c r="G47">
-        <v>-7.84475652262358</v>
+        <v>-3.191393731450273</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.314416357381234</v>
       </c>
       <c r="E48">
-        <v>-28.721943568311</v>
+        <v>-27.17048384480913</v>
       </c>
       <c r="F48">
-        <v>2.504677211246564</v>
+        <v>4.001790588530527</v>
       </c>
       <c r="G48">
-        <v>-7.733746234824446</v>
+        <v>-3.824121528422676</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.304856980153644</v>
       </c>
       <c r="E49">
-        <v>-27.65880731095226</v>
+        <v>-26.96006830004273</v>
       </c>
       <c r="F49">
-        <v>2.471776114742173</v>
+        <v>4.190833970258208</v>
       </c>
       <c r="G49">
-        <v>-7.775063376700975</v>
+        <v>-4.530611186051396</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.315693614783783</v>
       </c>
       <c r="E50">
-        <v>-27.85577781638989</v>
+        <v>-25.58393750469583</v>
       </c>
       <c r="F50">
-        <v>2.772234912146388</v>
+        <v>4.321179237823516</v>
       </c>
       <c r="G50">
-        <v>-7.578052271828795</v>
+        <v>-4.705204985229449</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.355321895428874</v>
       </c>
       <c r="E51">
-        <v>-27.68437507519956</v>
+        <v>-26.12068394340298</v>
       </c>
       <c r="F51">
-        <v>2.472760215216699</v>
+        <v>4.396812495168722</v>
       </c>
       <c r="G51">
-        <v>-8.422156361660626</v>
+        <v>-3.642476384113376</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.422635877654846</v>
       </c>
       <c r="E52">
-        <v>-26.54721638171144</v>
+        <v>-23.95554353627765</v>
       </c>
       <c r="F52">
-        <v>2.573870740402407</v>
+        <v>4.832608302107514</v>
       </c>
       <c r="G52">
-        <v>-7.785651878673303</v>
+        <v>-5.245451552548903</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.506425675765088</v>
       </c>
       <c r="E53">
-        <v>-26.40612271705445</v>
+        <v>-24.62553579418648</v>
       </c>
       <c r="F53">
-        <v>2.594174025445023</v>
+        <v>4.449644111384469</v>
       </c>
       <c r="G53">
-        <v>-8.268109571887816</v>
+        <v>-4.567295243085988</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.601659384584281</v>
       </c>
       <c r="E54">
-        <v>-26.00035786054517</v>
+        <v>-23.21191376253008</v>
       </c>
       <c r="F54">
-        <v>2.640269357941204</v>
+        <v>4.43147635750627</v>
       </c>
       <c r="G54">
-        <v>-8.720859085103116</v>
+        <v>-4.030900829877322</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.710117763240147</v>
       </c>
       <c r="E55">
-        <v>-25.84427041844878</v>
+        <v>-24.53944044635266</v>
       </c>
       <c r="F55">
-        <v>2.289233760391663</v>
+        <v>3.913753357695802</v>
       </c>
       <c r="G55">
-        <v>-8.571261631764912</v>
+        <v>-5.820298601212701</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.82496046987745</v>
       </c>
       <c r="E56">
-        <v>-25.25638845124703</v>
+        <v>-22.58405442678861</v>
       </c>
       <c r="F56">
-        <v>2.52633570536016</v>
+        <v>4.194702446029282</v>
       </c>
       <c r="G56">
-        <v>-8.550990244970663</v>
+        <v>-4.314401653834905</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.931581528414524</v>
       </c>
       <c r="E57">
-        <v>-25.00810127835448</v>
+        <v>-22.89081778454221</v>
       </c>
       <c r="F57">
-        <v>2.27365382627981</v>
+        <v>4.02930398344711</v>
       </c>
       <c r="G57">
-        <v>-8.820690251049221</v>
+        <v>-4.967666616547873</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.0363175476664</v>
       </c>
       <c r="E58">
-        <v>-24.43560706583078</v>
+        <v>-22.71676135758339</v>
       </c>
       <c r="F58">
-        <v>2.483994533933466</v>
+        <v>3.599387928333389</v>
       </c>
       <c r="G58">
-        <v>-8.658781654419982</v>
+        <v>-4.714490842242678</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.13463832579269</v>
       </c>
       <c r="E59">
-        <v>-23.98035504536567</v>
+        <v>-19.84582204857058</v>
       </c>
       <c r="F59">
-        <v>2.657396682361487</v>
+        <v>4.303773581955893</v>
       </c>
       <c r="G59">
-        <v>-8.77448737027068</v>
+        <v>-5.19961288736346</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.21287770354257</v>
       </c>
       <c r="E60">
-        <v>-24.12359067822829</v>
+        <v>-23.68717258116108</v>
       </c>
       <c r="F60">
-        <v>2.213577308759179</v>
+        <v>4.239972724592275</v>
       </c>
       <c r="G60">
-        <v>-9.282646871960324</v>
+        <v>-5.135008916079554</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.2737624021826</v>
       </c>
       <c r="E61">
-        <v>-23.44326897110795</v>
+        <v>-22.25052778764968</v>
       </c>
       <c r="F61">
-        <v>2.183467810402222</v>
+        <v>3.857555256355078</v>
       </c>
       <c r="G61">
-        <v>-9.180239947090055</v>
+        <v>-4.790290341487411</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.31765548102315</v>
       </c>
       <c r="E62">
-        <v>-22.48652468208541</v>
+        <v>-20.24339489559999</v>
       </c>
       <c r="F62">
-        <v>2.007532514456441</v>
+        <v>3.615055669389939</v>
       </c>
       <c r="G62">
-        <v>-9.244236892385464</v>
+        <v>-5.164854907384263</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.33718886447688</v>
       </c>
       <c r="E63">
-        <v>-23.10772716103561</v>
+        <v>-20.86446604880396</v>
       </c>
       <c r="F63">
-        <v>2.008929141897561</v>
+        <v>3.586170498054321</v>
       </c>
       <c r="G63">
-        <v>-9.340826211430839</v>
+        <v>-7.224346431385333</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.32887455526733</v>
       </c>
       <c r="E64">
-        <v>-22.08429203530211</v>
+        <v>-20.44345382031085</v>
       </c>
       <c r="F64">
-        <v>2.024679719694391</v>
+        <v>3.736762721678854</v>
       </c>
       <c r="G64">
-        <v>-9.550276427234873</v>
+        <v>-6.56301950730081</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.30005490850511</v>
       </c>
       <c r="E65">
-        <v>-22.76583643040451</v>
+        <v>-19.29933939074694</v>
       </c>
       <c r="F65">
-        <v>2.008554719831495</v>
+        <v>3.783038638268845</v>
       </c>
       <c r="G65">
-        <v>-9.884787121555584</v>
+        <v>-7.798090989605157</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.2503299604483</v>
       </c>
       <c r="E66">
-        <v>-22.18560758427572</v>
+        <v>-21.32071433355076</v>
       </c>
       <c r="F66">
-        <v>2.11096909530921</v>
+        <v>3.59886440013482</v>
       </c>
       <c r="G66">
-        <v>-9.731265327232284</v>
+        <v>-6.292023418706271</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.17139517917067</v>
       </c>
       <c r="E67">
-        <v>-22.26079383822507</v>
+        <v>-20.54350139656231</v>
       </c>
       <c r="F67">
-        <v>1.998037767285553</v>
+        <v>3.127016387091388</v>
       </c>
       <c r="G67">
-        <v>-9.856020652143933</v>
+        <v>-7.578029303277878</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.07603056827722</v>
       </c>
       <c r="E68">
-        <v>-22.15947828925146</v>
+        <v>-17.3374595394559</v>
       </c>
       <c r="F68">
-        <v>1.61899175437775</v>
+        <v>3.364098451242218</v>
       </c>
       <c r="G68">
-        <v>-9.996178031055614</v>
+        <v>-6.012650371470469</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.967170079750556</v>
       </c>
       <c r="E69">
-        <v>-21.39206497001561</v>
+        <v>-20.17294995393667</v>
       </c>
       <c r="F69">
-        <v>1.314135982799476</v>
+        <v>3.502992470404416</v>
       </c>
       <c r="G69">
-        <v>-10.29188828043589</v>
+        <v>-7.075424909688375</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.839171031123387</v>
       </c>
       <c r="E70">
-        <v>-21.15913838095708</v>
+        <v>-18.52416426706194</v>
       </c>
       <c r="F70">
-        <v>1.609740547223285</v>
+        <v>2.939121122583987</v>
       </c>
       <c r="G70">
-        <v>-9.960514433926008</v>
+        <v>-7.080159712398654</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.69985625277276</v>
       </c>
       <c r="E71">
-        <v>-21.25163246256374</v>
+        <v>-19.36582191765355</v>
       </c>
       <c r="F71">
-        <v>1.556052399113043</v>
+        <v>3.046532210235388</v>
       </c>
       <c r="G71">
-        <v>-9.984339383669136</v>
+        <v>-6.761379194233921</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.556544736112448</v>
       </c>
       <c r="E72">
-        <v>-21.21998295772414</v>
+        <v>-17.75228587245453</v>
       </c>
       <c r="F72">
-        <v>1.445949117402544</v>
+        <v>3.300121979989206</v>
       </c>
       <c r="G72">
-        <v>-9.902203845593116</v>
+        <v>-7.629528075653363</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.408622441832398</v>
       </c>
       <c r="E73">
-        <v>-21.16396573424926</v>
+        <v>-20.10304390068026</v>
       </c>
       <c r="F73">
-        <v>1.10888476446862</v>
+        <v>2.90743109922249</v>
       </c>
       <c r="G73">
-        <v>-10.41372331815963</v>
+        <v>-7.298652974820517</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.255563621924027</v>
       </c>
       <c r="E74">
-        <v>-21.38375974868555</v>
+        <v>-18.25302641432669</v>
       </c>
       <c r="F74">
-        <v>1.275008876895644</v>
+        <v>2.974951326224677</v>
       </c>
       <c r="G74">
-        <v>-9.795380396503834</v>
+        <v>-6.807624730892735</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.10905148823284</v>
       </c>
       <c r="E75">
-        <v>-22.36813225762888</v>
+        <v>-19.96201363465938</v>
       </c>
       <c r="F75">
-        <v>0.9113191389009375</v>
+        <v>2.518063628475804</v>
       </c>
       <c r="G75">
-        <v>-10.20654370767473</v>
+        <v>-7.204734570124532</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.971347155219936</v>
       </c>
       <c r="E76">
-        <v>-22.08191005797407</v>
+        <v>-19.27606303434752</v>
       </c>
       <c r="F76">
-        <v>0.9528783314993887</v>
+        <v>2.331618006923303</v>
       </c>
       <c r="G76">
-        <v>-9.349780665066563</v>
+        <v>-7.77727492003204</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.834454233063767</v>
       </c>
       <c r="E77">
-        <v>-22.05676344180948</v>
+        <v>-18.92747016218507</v>
       </c>
       <c r="F77">
-        <v>1.028284616176228</v>
+        <v>2.369910118485113</v>
       </c>
       <c r="G77">
-        <v>-9.641264701078276</v>
+        <v>-6.796852480513078</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.711055390236968</v>
       </c>
       <c r="E78">
-        <v>-22.46500084512695</v>
+        <v>-19.51067874421091</v>
       </c>
       <c r="F78">
-        <v>0.9050699352142181</v>
+        <v>2.064832344442888</v>
       </c>
       <c r="G78">
-        <v>-9.804666253517063</v>
+        <v>-7.355332796038366</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.603892181987582</v>
       </c>
       <c r="E79">
-        <v>-22.28014400765985</v>
+        <v>-21.24903764695735</v>
       </c>
       <c r="F79">
-        <v>0.8094415455002375</v>
+        <v>2.137271417082899</v>
       </c>
       <c r="G79">
-        <v>-9.281058760725553</v>
+        <v>-7.6658282297655</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.507458719749286</v>
       </c>
       <c r="E80">
-        <v>-22.88205065886336</v>
+        <v>-21.92736682551431</v>
       </c>
       <c r="F80">
-        <v>0.5780379398955985</v>
+        <v>1.858570517880617</v>
       </c>
       <c r="G80">
-        <v>-8.998808082182119</v>
+        <v>-6.237879981753873</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.425012258757135</v>
       </c>
       <c r="E81">
-        <v>-23.33089941708162</v>
+        <v>-21.29727495208705</v>
       </c>
       <c r="F81">
-        <v>0.6184283060886996</v>
+        <v>2.23435276322139</v>
       </c>
       <c r="G81">
-        <v>-9.167338183918318</v>
+        <v>-5.995827548535196</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.361872437130732</v>
       </c>
       <c r="E82">
-        <v>-24.04911992317215</v>
+        <v>-22.12796463863208</v>
       </c>
       <c r="F82">
-        <v>0.6610983393743048</v>
+        <v>1.611380714680828</v>
       </c>
       <c r="G82">
-        <v>-8.479328366112391</v>
+        <v>-5.835021442349929</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.314702158247865</v>
       </c>
       <c r="E83">
-        <v>-25.01243049950581</v>
+        <v>-23.26441689017501</v>
       </c>
       <c r="F83">
-        <v>0.5471224400557181</v>
+        <v>1.977759333265021</v>
       </c>
       <c r="G83">
-        <v>-8.558563304329862</v>
+        <v>-6.479830697104208</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.275993115677311</v>
       </c>
       <c r="E84">
-        <v>-25.38929010642413</v>
+        <v>-23.97747040742279</v>
       </c>
       <c r="F84">
-        <v>0.473881507769797</v>
+        <v>2.185977763632705</v>
       </c>
       <c r="G84">
-        <v>-8.502920349124798</v>
+        <v>-5.979818468546665</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.252662291264297</v>
       </c>
       <c r="E85">
-        <v>-27.04085627633957</v>
+        <v>-23.37029261247434</v>
       </c>
       <c r="F85">
-        <v>0.424657431593242</v>
+        <v>1.885434472753405</v>
       </c>
       <c r="G85">
-        <v>-8.341618778484056</v>
+        <v>-6.250752213931575</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.241261270032409</v>
       </c>
       <c r="E86">
-        <v>-26.93456393443153</v>
+        <v>-25.46637831945671</v>
       </c>
       <c r="F86">
-        <v>0.3572357803119874</v>
+        <v>1.934444001772635</v>
       </c>
       <c r="G86">
-        <v>-8.100219308355708</v>
+        <v>-5.278427829221322</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.228928288614155</v>
       </c>
       <c r="E87">
-        <v>-28.62422815617349</v>
+        <v>-27.52905294521048</v>
       </c>
       <c r="F87">
-        <v>0.5371107916254833</v>
+        <v>1.770137327427353</v>
       </c>
       <c r="G87">
-        <v>-7.542529767226246</v>
+        <v>-4.737196895434035</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.218849326845035</v>
       </c>
       <c r="E88">
-        <v>-29.59256081018166</v>
+        <v>-27.25389380755641</v>
       </c>
       <c r="F88">
-        <v>0.001051050986644821</v>
+        <v>1.165492079306327</v>
       </c>
       <c r="G88">
-        <v>-7.787282645788347</v>
+        <v>-5.070119478519975</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.208118767497432</v>
       </c>
       <c r="E89">
-        <v>-31.09118003472503</v>
+        <v>-29.91099178121602</v>
       </c>
       <c r="F89">
-        <v>0.3813760631643706</v>
+        <v>1.441709533035016</v>
       </c>
       <c r="G89">
-        <v>-7.866199305514551</v>
+        <v>-4.340694082190736</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.187319001375627</v>
       </c>
       <c r="E90">
-        <v>-32.39365746457418</v>
+        <v>-30.82994142617055</v>
       </c>
       <c r="F90">
-        <v>0.2660648355924711</v>
+        <v>1.689489133825599</v>
       </c>
       <c r="G90">
-        <v>-7.388240167058036</v>
+        <v>-4.823099275860298</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.153076754303736</v>
       </c>
       <c r="E91">
-        <v>-34.53162249917948</v>
+        <v>-33.10448750108419</v>
       </c>
       <c r="F91">
-        <v>-0.06507751877883972</v>
+        <v>1.875691215361677</v>
       </c>
       <c r="G91">
-        <v>-7.511893001525711</v>
+        <v>-4.728432752648758</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.108357781653373</v>
       </c>
       <c r="E92">
-        <v>-35.59854456080863</v>
+        <v>-36.11305166366411</v>
       </c>
       <c r="F92">
-        <v>-0.2359092431559734</v>
+        <v>0.9946164514568446</v>
       </c>
       <c r="G92">
-        <v>-7.211218263925995</v>
+        <v>-5.256565049970742</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.050031098015644</v>
       </c>
       <c r="E93">
-        <v>-36.66819502802741</v>
+        <v>-34.92791605230172</v>
       </c>
       <c r="F93">
-        <v>-0.0186872874872618</v>
+        <v>0.9593992396942265</v>
       </c>
       <c r="G93">
-        <v>-6.896965831513295</v>
+        <v>-4.927967116900152</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.969879589099317</v>
       </c>
       <c r="E94">
-        <v>-38.52118319333002</v>
+        <v>-36.68144081449985</v>
       </c>
       <c r="F94">
-        <v>-0.1245576117694554</v>
+        <v>0.7851571267197672</v>
       </c>
       <c r="G94">
-        <v>-7.754828083343879</v>
+        <v>-4.463972857400633</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.876677898345051</v>
       </c>
       <c r="E95">
-        <v>-39.51141554763928</v>
+        <v>-38.63396710272805</v>
       </c>
       <c r="F95">
-        <v>-0.3006121926212399</v>
+        <v>1.09214014578843</v>
       </c>
       <c r="G95">
-        <v>-7.834017084459518</v>
+        <v>-5.159867450613906</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.770788845851218</v>
       </c>
       <c r="E96">
-        <v>-42.50363418328852</v>
+        <v>-40.68230457977354</v>
       </c>
       <c r="F96">
-        <v>-0.4591849078043437</v>
+        <v>0.5246902507879075</v>
       </c>
       <c r="G96">
-        <v>-8.084180697373142</v>
+        <v>-5.150991746295609</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.64686639701178</v>
       </c>
       <c r="E97">
-        <v>-44.32274483453974</v>
+        <v>-43.82246393277936</v>
       </c>
       <c r="F97">
-        <v>-0.5835253400667579</v>
+        <v>0.5807342757917109</v>
       </c>
       <c r="G97">
-        <v>-8.083737732462618</v>
+        <v>-4.774084388205313</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.51268251872872</v>
       </c>
       <c r="E98">
-        <v>-45.73518719871714</v>
+        <v>-44.45669935992363</v>
       </c>
       <c r="F98">
-        <v>-0.7292823831611505</v>
+        <v>1.025777976415357</v>
       </c>
       <c r="G98">
-        <v>-8.363826085998378</v>
+        <v>-5.157180130156721</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.374950260140754</v>
       </c>
       <c r="E99">
-        <v>-47.70112682695606</v>
+        <v>-45.83247467006093</v>
       </c>
       <c r="F99">
-        <v>-0.7206110331886453</v>
+        <v>0.8206294756424477</v>
       </c>
       <c r="G99">
-        <v>-8.560417194510949</v>
+        <v>-5.731147811442588</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.23349563769487</v>
       </c>
       <c r="E100">
-        <v>-50.39310876801526</v>
+        <v>-46.94335915735655</v>
       </c>
       <c r="F100">
-        <v>-0.8309876761420683</v>
+        <v>-0.3414888104797844</v>
       </c>
       <c r="G100">
-        <v>-8.720803304336606</v>
+        <v>-6.169830727832549</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.092534415670364</v>
       </c>
       <c r="E101">
-        <v>-50.9685215820369</v>
+        <v>-50.58368053968005</v>
       </c>
       <c r="F101">
-        <v>-1.207757335426979</v>
+        <v>0.1150484878577044</v>
       </c>
       <c r="G101">
-        <v>-9.113900209601201</v>
+        <v>-5.47639705078886</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.959943621266642</v>
       </c>
       <c r="E102">
-        <v>-54.05493926975669</v>
+        <v>-53.36746823429675</v>
       </c>
       <c r="F102">
-        <v>-1.264291753933239</v>
+        <v>-0.06418702382083025</v>
       </c>
       <c r="G102">
-        <v>-8.996229042036395</v>
+        <v>-6.18625324173757</v>
       </c>
     </row>
   </sheetData>
